--- a/artfynd/A 12196-2022 artfynd.xlsx
+++ b/artfynd/A 12196-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12196-2022 artfynd.xlsx
+++ b/artfynd/A 12196-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112354194</v>
+        <v>112354197</v>
       </c>
       <c r="B2" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546252</v>
+        <v>546193</v>
       </c>
       <c r="R2" t="n">
-        <v>7046000</v>
+        <v>7046053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112354193</v>
+        <v>112354195</v>
       </c>
       <c r="B3" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112354188</v>
+        <v>112354189</v>
       </c>
       <c r="B4" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546256</v>
+        <v>546436</v>
       </c>
       <c r="R4" t="n">
-        <v>7046082</v>
+        <v>7046009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,49 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112354201</v>
+        <v>112354193</v>
       </c>
       <c r="B5" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546068</v>
+        <v>546252</v>
       </c>
       <c r="R5" t="n">
-        <v>7046096</v>
+        <v>7046000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112354195</v>
+        <v>112354196</v>
       </c>
       <c r="B6" t="n">
-        <v>90034</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546252</v>
+        <v>546193</v>
       </c>
       <c r="R6" t="n">
-        <v>7046000</v>
+        <v>7046053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112354189</v>
+        <v>112354188</v>
       </c>
       <c r="B7" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546436</v>
+        <v>546256</v>
       </c>
       <c r="R7" t="n">
-        <v>7046010</v>
+        <v>7046082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112354197</v>
+        <v>112354194</v>
       </c>
       <c r="B8" t="n">
-        <v>89875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546193</v>
+        <v>546252</v>
       </c>
       <c r="R8" t="n">
-        <v>7046053</v>
+        <v>7046000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1392,12 +1357,7 @@
         <v>112354198</v>
       </c>
       <c r="B9" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,7 +1389,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546159</v>
+        <v>546158</v>
       </c>
       <c r="R9" t="n">
         <v>7046063</v>
@@ -1479,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112354196</v>
+        <v>112354201</v>
       </c>
       <c r="B10" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546193</v>
+        <v>546068</v>
       </c>
       <c r="R10" t="n">
-        <v>7046053</v>
+        <v>7046095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1596,12 +1551,7 @@
         <v>112354190</v>
       </c>
       <c r="B11" t="n">
-        <v>97114</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,7 +1586,7 @@
         <v>546436</v>
       </c>
       <c r="R11" t="n">
-        <v>7046010</v>
+        <v>7046009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1698,12 +1648,7 @@
         <v>112354200</v>
       </c>
       <c r="B12" t="n">
-        <v>97114</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1683,7 @@
         <v>546068</v>
       </c>
       <c r="R12" t="n">
-        <v>7046096</v>
+        <v>7046095</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 12196-2022 artfynd.xlsx
+++ b/artfynd/A 12196-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354189</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354194</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354198</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354201</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354190</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>